--- a/data/pediatric.xlsx
+++ b/data/pediatric.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anthonygagnon/code/DiffusionCompass/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23916C1B-6395-BD45-B796-EBC051F889CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{351E7112-779F-A245-92B3-06E29B398062}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25600" yWindow="600" windowWidth="25600" windowHeight="26960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -479,9 +479,6 @@
     <t>QUALITY CONTROL</t>
   </si>
   <si>
-    <t>outlierDetection</t>
-  </si>
-  <si>
     <t>CONNECTOMICS</t>
   </si>
   <si>
@@ -612,6 +609,9 @@
   </si>
   <si>
     <t>QC - automated outlier detection</t>
+  </si>
+  <si>
+    <t>qcOutlier</t>
   </si>
 </sst>
 </file>
@@ -1086,10 +1086,10 @@
         <v>99</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="84" x14ac:dyDescent="0.2">
@@ -1103,10 +1103,10 @@
         <v>100</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
@@ -1117,21 +1117,21 @@
         <v>76</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>9</v>
@@ -1291,7 +1291,7 @@
         <v>108</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E14" s="14" t="s">
         <v>107</v>
@@ -1325,10 +1325,10 @@
         <v>111</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
@@ -1356,10 +1356,10 @@
         <v>113</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E18" s="14" t="s">
         <v>114</v>
@@ -1390,13 +1390,13 @@
         <v>19</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
@@ -1475,10 +1475,10 @@
         <v>120</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D25" s="14" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E25" s="14" t="s">
         <v>121</v>
@@ -1586,13 +1586,13 @@
         <v>124</v>
       </c>
       <c r="C32" s="14" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D32" s="14" t="s">
         <v>125</v>
       </c>
       <c r="E32" s="14" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.2">
@@ -1620,13 +1620,13 @@
         <v>130</v>
       </c>
       <c r="C34" s="14" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D34" s="14" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E34" s="14" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.2">
@@ -1776,10 +1776,10 @@
         <v>144</v>
       </c>
       <c r="D43" s="14" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E43" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.2">
@@ -2001,7 +2001,7 @@
         <v>57</v>
       </c>
       <c r="B58" s="13" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C58" s="14" t="s">
         <v>9</v>
@@ -2015,10 +2015,10 @@
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A59" s="12" t="s">
-        <v>152</v>
+        <v>196</v>
       </c>
       <c r="B59" s="13" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C59" s="14" t="s">
         <v>9</v>
@@ -2032,7 +2032,7 @@
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A60" s="11" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B60" s="11"/>
       <c r="C60" s="11"/>
@@ -2058,10 +2058,10 @@
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A62" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="B62" s="13" t="s">
         <v>191</v>
-      </c>
-      <c r="B62" s="13" t="s">
-        <v>192</v>
       </c>
       <c r="C62" s="14" t="s">
         <v>9</v>
@@ -2075,10 +2075,10 @@
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A63" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="B63" s="13" t="s">
         <v>193</v>
-      </c>
-      <c r="B63" s="13" t="s">
-        <v>194</v>
       </c>
       <c r="C63" s="14" t="s">
         <v>9</v>
@@ -2092,7 +2092,7 @@
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A64" s="11" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B64" s="11"/>
       <c r="C64" s="11"/>
@@ -2118,10 +2118,10 @@
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A66" s="12" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B66" s="13" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C66" s="14" t="s">
         <v>9</v>
@@ -2135,7 +2135,7 @@
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A67" s="11" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B67" s="11"/>
       <c r="C67" s="11"/>
@@ -2144,10 +2144,10 @@
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A68" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="B68" s="13" t="s">
         <v>155</v>
-      </c>
-      <c r="B68" s="13" t="s">
-        <v>156</v>
       </c>
       <c r="C68" s="14" t="s">
         <v>9</v>
@@ -2161,10 +2161,10 @@
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A69" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="B69" s="13" t="s">
         <v>157</v>
-      </c>
-      <c r="B69" s="13" t="s">
-        <v>158</v>
       </c>
       <c r="C69" s="14" t="s">
         <v>9</v>
@@ -2178,10 +2178,10 @@
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A70" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="B70" s="13" t="s">
         <v>159</v>
-      </c>
-      <c r="B70" s="13" t="s">
-        <v>160</v>
       </c>
       <c r="C70" s="14" t="s">
         <v>9</v>
@@ -2195,7 +2195,7 @@
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A71" s="11" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B71" s="11"/>
       <c r="C71" s="11"/>
@@ -2210,13 +2210,13 @@
         <v>97</v>
       </c>
       <c r="C72" s="14" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D72" s="14" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E72" s="14" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
   </sheetData>
@@ -2409,10 +2409,10 @@
         <v>116</v>
       </c>
       <c r="C12" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="D12" s="13" t="s">
         <v>183</v>
-      </c>
-      <c r="D12" s="13" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
